--- a/data/trans_orig/IP19C09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Estudios-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38892</t>
+          <t>39892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86802</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220570</t>
+          <t>219814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227062</t>
+          <t>227038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230524</t>
+          <t>231298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240631</t>
+          <t>240653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455448</t>
+          <t>455899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>466425</t>
+          <t>466804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70650</t>
+          <t>70712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>67407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72503</t>
+          <t>72505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141361</t>
+          <t>140947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147535</t>
+          <t>147529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340926</t>
+          <t>341599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348698</t>
+          <t>348994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344655</t>
+          <t>344290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>355122</t>
+          <t>354737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689807</t>
+          <t>688969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702412</t>
+          <t>702151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43770</t>
+          <t>43548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37550</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83252</t>
+          <t>82497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88960</t>
+          <t>88945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208598</t>
+          <t>207958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216282</t>
+          <t>216074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227579</t>
+          <t>227452</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234030</t>
+          <t>234094</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>439361</t>
+          <t>439919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>448958</t>
+          <t>449027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78355</t>
+          <t>78118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76628</t>
+          <t>77517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158192</t>
+          <t>158678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163737</t>
+          <t>163738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335439</t>
+          <t>334722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343937</t>
+          <t>343778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348197</t>
+          <t>348458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357450</t>
+          <t>357360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>687756</t>
+          <t>687835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699842</t>
+          <t>699857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15731</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230549</t>
+          <t>230480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238940</t>
+          <t>238535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235648</t>
+          <t>235625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242883</t>
+          <t>242859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>469746</t>
+          <t>469391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>480443</t>
+          <t>479983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77155</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>83733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76737</t>
+          <t>75983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84266</t>
+          <t>83842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157501</t>
+          <t>157440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166982</t>
+          <t>166746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>332222</t>
+          <t>332429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342418</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340855</t>
+          <t>340852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351497</t>
+          <t>351586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677919</t>
+          <t>678274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691793</t>
+          <t>692042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>603</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2999</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3078</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3451</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42288</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39851</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42288</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>39892</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,01%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>133</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86365</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8585</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14235</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3490</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8508</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8585</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5070</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14425</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>237138</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>231488</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>241044</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>224832</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>219814</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>227038</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>220529</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>227065</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>237138</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>231298</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>240653</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455899</t>
+          <t>454416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>466804</t>
+          <t>466324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1403</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4971</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4341</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5710</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7567</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3304</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7853</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1521,107 +1521,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71215</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68444</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>74280</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70712</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>71342</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,15%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71215</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67407</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>72505</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>145496</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>141233</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>147548</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>145496</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>140947</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>147529</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,72%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1639,52 +1639,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7123</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18017</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4893</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9353</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6994</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17441</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>350641</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>343714</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>354608</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>515</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>346037</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>341599</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>348994</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>341577</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>348881</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>350641</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>344290</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>354737</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688969</t>
+          <t>689001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702151</t>
+          <t>701995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3042</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7372</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41243</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36655</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>45981</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43548</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43286</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>46590</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41243</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35591</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>82,84%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>123</t>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82497</t>
+          <t>82987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88945</t>
+          <t>88940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46590</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46590</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46590</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3528</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7749</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4275</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9674</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8780</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7946</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>231870</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>227649</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>234093</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>213357</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>207958</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>216074</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>208852</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>215972</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>231870</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>227452</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>234094</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>439919</t>
+          <t>438502</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>449027</t>
+          <t>448595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>235398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>235398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>235398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>217632</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>217632</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>217632</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>235398</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>235398</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>235398</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4091</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>764</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4113</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3860</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4608</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80797</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>78034</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>81467</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78118</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78371</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>82231</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>80797</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>77517</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,39%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>230</t>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158678</t>
+          <t>158549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163738</t>
+          <t>163733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>82231</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>82231</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>82231</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12686</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2675</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11731</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12029</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>353911</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>347801</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>357541</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>340805</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>334722</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>343778</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>336251</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>343974</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>353911</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>348458</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>357360</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>687835</t>
+          <t>687569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699857</t>
+          <t>699531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>346453</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>346453</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>346453</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,107 +3928,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3070</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26098</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21025</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18617</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19064</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>21589</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,39%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26098</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>68</t>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21589</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>21589</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>21589</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>26098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>26098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,107 +4271,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4228</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8707</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5266</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2508</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10563</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11136</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>9494</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>5028</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>15912</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4228</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>9494</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>5494</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>16086</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4384,107 +4384,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>240207</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>235728</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>242947</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>235777</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>230480</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>238535</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>229907</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>238929</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>475983</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>469565</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>480449</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>98,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>240207</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>235625</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>242859</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>475983</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>469391</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>479983</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>244435</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>244435</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>244435</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>353</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>241043</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>241043</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>241043</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>244435</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>244435</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>244435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4388</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8781</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3012</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7219</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6859</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4388</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9762</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81357</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76964</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84356</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>81539</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77332</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83733</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77692</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>83739</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>81357</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75983</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>83842</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>157306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166746</t>
+          <t>166701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>85745</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>85745</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>85745</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>85745</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>85745</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>85745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4962,67 +4962,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4364</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>8842</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4889</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14753</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4151</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14237</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4692</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15426</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>347662</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>341639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>351914</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>338340</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>332429</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>342293</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>332945</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>343031</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>347662</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>340852</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>351586</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678274</t>
+          <t>678478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>692042</t>
+          <t>692081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>347182</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>347182</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>347182</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
